--- a/IA_CCBS_BANK_SIDE/Customer/CCBS_UpdateIndividualCustomer.xlsx
+++ b/IA_CCBS_BANK_SIDE/Customer/CCBS_UpdateIndividualCustomer.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20399"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sw\Relational_Files\Asset Bank Interfaces_New\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kmilos\source\repos\iApply_CCBS_API\IA_CCBS_BANK_SIDE\Customer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C591187-B726-4FDB-9810-FF86F2735F2C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5B0FDE-3533-4757-9638-95F3B3F7ABCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11025" activeTab="1" xr2:uid="{71FA6D81-4DAE-49DF-BD64-C0A351CD7C3B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{71FA6D81-4DAE-49DF-BD64-C0A351CD7C3B}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="259">
   <si>
     <t>First Name</t>
   </si>
@@ -756,13 +756,67 @@
   </si>
   <si>
     <t>AddressSerialNum</t>
+  </si>
+  <si>
+    <t>AMLFields</t>
+  </si>
+  <si>
+    <t>Class with next fields in extended categories</t>
+  </si>
+  <si>
+    <t>estTransLevel</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>Estimated Transaction Level</t>
+  </si>
+  <si>
+    <t>fundsSD</t>
+  </si>
+  <si>
+    <t>string[]</t>
+  </si>
+  <si>
+    <t>Funds Source / Destination - multiple selection field</t>
+  </si>
+  <si>
+    <t>polExp</t>
+  </si>
+  <si>
+    <t>Political exposure</t>
+  </si>
+  <si>
+    <t>repRisk</t>
+  </si>
+  <si>
+    <t>Reputation Risk</t>
+  </si>
+  <si>
+    <t>busRelPurpose</t>
+  </si>
+  <si>
+    <t>Business Relation Purpose</t>
+  </si>
+  <si>
+    <t>typeOfProduct</t>
+  </si>
+  <si>
+    <t>type of product</t>
+  </si>
+  <si>
+    <t>clientStatus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Client status </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -826,6 +880,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="161"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -853,7 +915,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -891,13 +953,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFED7D31"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFED7D31"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFED7D31"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -914,27 +996,33 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="20% - Accent4" xfId="1" builtinId="42"/>
@@ -996,9 +1084,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1036,7 +1124,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1142,7 +1230,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1284,7 +1372,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1293,20 +1381,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89993E1D-86FC-4340-878F-FAF98EE683C1}">
   <dimension ref="B2:C14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.5546875" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="3"/>
       <c r="C2" s="4" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>185</v>
       </c>
@@ -1314,7 +1402,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>187</v>
       </c>
@@ -1322,7 +1410,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>189</v>
       </c>
@@ -1330,11 +1418,11 @@
         <v>190</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>191</v>
       </c>
@@ -1342,11 +1430,11 @@
         <v>192</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B8" s="4"/>
       <c r="C8" s="5"/>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>193</v>
       </c>
@@ -1354,7 +1442,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>195</v>
       </c>
@@ -1362,15 +1450,15 @@
         <v>196</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B11" s="4"/>
       <c r="C11" s="5"/>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B12" s="4"/>
       <c r="C12" s="5"/>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
         <v>197</v>
       </c>
@@ -1378,7 +1466,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B14" s="4"/>
       <c r="C14" s="5"/>
     </row>
@@ -1389,18 +1477,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79128A65-9683-4A44-8F1C-885040A9EB1A}">
-  <dimension ref="A1:G116"/>
-  <sheetFormatPr defaultColWidth="110" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G124"/>
+  <sheetFormatPr defaultColWidth="110" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30" style="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="87.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="87.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>179</v>
       </c>
@@ -1421,7 +1509,7 @@
       </c>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="9">
         <v>1</v>
       </c>
@@ -1439,7 +1527,7 @@
       </c>
       <c r="F2" s="7"/>
     </row>
-    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -1457,7 +1545,7 @@
       </c>
       <c r="F3" s="7"/>
     </row>
-    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -1475,7 +1563,7 @@
       </c>
       <c r="F4" s="7"/>
     </row>
-    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
         <v>4</v>
       </c>
@@ -1493,7 +1581,7 @@
       </c>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
         <v>5</v>
       </c>
@@ -1511,7 +1599,7 @@
       </c>
       <c r="F6" s="7"/>
     </row>
-    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9">
         <v>6</v>
       </c>
@@ -1529,7 +1617,7 @@
       </c>
       <c r="F7" s="7"/>
     </row>
-    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>7</v>
       </c>
@@ -1547,7 +1635,7 @@
       </c>
       <c r="F8" s="7"/>
     </row>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
         <v>8</v>
       </c>
@@ -1567,7 +1655,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>9</v>
       </c>
@@ -1587,7 +1675,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
         <v>10</v>
       </c>
@@ -1605,7 +1693,7 @@
       </c>
       <c r="F11" s="7"/>
     </row>
-    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>11</v>
       </c>
@@ -1623,7 +1711,7 @@
       </c>
       <c r="F12" s="7"/>
     </row>
-    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>12</v>
       </c>
@@ -1641,7 +1729,7 @@
       </c>
       <c r="F13" s="7"/>
     </row>
-    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>13</v>
       </c>
@@ -1659,7 +1747,7 @@
       </c>
       <c r="F14" s="7"/>
     </row>
-    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
         <v>14</v>
       </c>
@@ -1677,7 +1765,7 @@
       </c>
       <c r="F15" s="7"/>
     </row>
-    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>15</v>
       </c>
@@ -1695,7 +1783,7 @@
       </c>
       <c r="F16" s="7"/>
     </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
         <v>16</v>
       </c>
@@ -1713,7 +1801,7 @@
       </c>
       <c r="F17" s="7"/>
     </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>17</v>
       </c>
@@ -1731,7 +1819,7 @@
       </c>
       <c r="F18" s="7"/>
     </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9">
         <v>18</v>
       </c>
@@ -1749,7 +1837,7 @@
       </c>
       <c r="F19" s="7"/>
     </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>19</v>
       </c>
@@ -1767,7 +1855,7 @@
       </c>
       <c r="F20" s="7"/>
     </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="9">
         <v>20</v>
       </c>
@@ -1783,7 +1871,7 @@
       </c>
       <c r="F21" s="7"/>
     </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="9">
         <v>21</v>
       </c>
@@ -1801,7 +1889,7 @@
       </c>
       <c r="F22" s="7"/>
     </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="9">
         <v>22</v>
       </c>
@@ -1819,7 +1907,7 @@
       </c>
       <c r="F23" s="7"/>
     </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="9">
         <v>23</v>
       </c>
@@ -1837,7 +1925,7 @@
       </c>
       <c r="F24" s="7"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="9">
         <v>24</v>
       </c>
@@ -1855,7 +1943,7 @@
       </c>
       <c r="F25" s="7"/>
     </row>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9">
         <v>25</v>
       </c>
@@ -1873,7 +1961,7 @@
       </c>
       <c r="F26" s="7"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="9">
         <v>26</v>
       </c>
@@ -1891,7 +1979,7 @@
       </c>
       <c r="F27" s="7"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="9">
         <v>27</v>
       </c>
@@ -1909,7 +1997,7 @@
       </c>
       <c r="F28" s="7"/>
     </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="9">
         <v>28</v>
       </c>
@@ -1927,7 +2015,7 @@
       </c>
       <c r="F29" s="7"/>
     </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="9">
         <v>29</v>
       </c>
@@ -1945,7 +2033,7 @@
       </c>
       <c r="F30" s="7"/>
     </row>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="9">
         <v>30</v>
       </c>
@@ -1963,7 +2051,7 @@
       </c>
       <c r="F31" s="7"/>
     </row>
-    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="9">
         <v>31</v>
       </c>
@@ -1981,7 +2069,7 @@
       </c>
       <c r="F32" s="7"/>
     </row>
-    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="9">
         <v>32</v>
       </c>
@@ -1999,7 +2087,7 @@
       </c>
       <c r="F33" s="7"/>
     </row>
-    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="9">
         <v>33</v>
       </c>
@@ -2017,7 +2105,7 @@
       </c>
       <c r="F34" s="7"/>
     </row>
-    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="9">
         <v>34</v>
       </c>
@@ -2035,7 +2123,7 @@
       </c>
       <c r="F35" s="7"/>
     </row>
-    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="9">
         <v>35</v>
       </c>
@@ -2053,7 +2141,7 @@
       </c>
       <c r="F36" s="7"/>
     </row>
-    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="9">
         <v>36</v>
       </c>
@@ -2069,7 +2157,7 @@
       </c>
       <c r="F37" s="7"/>
     </row>
-    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="9">
         <v>37</v>
       </c>
@@ -2085,7 +2173,7 @@
       </c>
       <c r="F38" s="7"/>
     </row>
-    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="9">
         <v>38</v>
       </c>
@@ -2103,7 +2191,7 @@
       </c>
       <c r="F39" s="7"/>
     </row>
-    <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="9">
         <v>40</v>
       </c>
@@ -2121,7 +2209,7 @@
       </c>
       <c r="F40" s="7"/>
     </row>
-    <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="9">
         <v>41</v>
       </c>
@@ -2139,7 +2227,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="9">
         <v>42</v>
       </c>
@@ -2155,7 +2243,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="9">
         <v>43</v>
       </c>
@@ -2171,7 +2259,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="9">
         <v>45</v>
       </c>
@@ -2189,7 +2277,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="9">
         <v>46</v>
       </c>
@@ -2207,7 +2295,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="9">
         <v>47</v>
       </c>
@@ -2225,7 +2313,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="9">
         <v>49</v>
       </c>
@@ -2243,7 +2331,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="9">
         <v>50</v>
       </c>
@@ -2261,7 +2349,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="9">
         <v>51</v>
       </c>
@@ -2279,7 +2367,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="9">
         <v>53</v>
       </c>
@@ -2297,7 +2385,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="9">
         <v>54</v>
       </c>
@@ -2315,7 +2403,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="9">
         <v>55</v>
       </c>
@@ -2333,7 +2421,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="9">
         <v>57</v>
       </c>
@@ -2351,7 +2439,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="9">
         <v>58</v>
       </c>
@@ -2369,7 +2457,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="9">
         <v>59</v>
       </c>
@@ -2387,7 +2475,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="9">
         <v>61</v>
       </c>
@@ -2405,7 +2493,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="9">
         <v>62</v>
       </c>
@@ -2423,7 +2511,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="9">
         <v>63</v>
       </c>
@@ -2441,7 +2529,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="9">
         <v>65</v>
       </c>
@@ -2459,7 +2547,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="9">
         <v>66</v>
       </c>
@@ -2477,7 +2565,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="9">
         <v>67</v>
       </c>
@@ -2495,7 +2583,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="9">
         <v>69</v>
       </c>
@@ -2513,7 +2601,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="9">
         <v>70</v>
       </c>
@@ -2531,7 +2619,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="9">
         <v>71</v>
       </c>
@@ -2549,7 +2637,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="9">
         <v>73</v>
       </c>
@@ -2567,7 +2655,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="9">
         <v>74</v>
       </c>
@@ -2585,7 +2673,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="9">
         <v>75</v>
       </c>
@@ -2603,7 +2691,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="9">
         <v>77</v>
       </c>
@@ -2621,7 +2709,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="9">
         <v>78</v>
       </c>
@@ -2639,7 +2727,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="9">
         <v>79</v>
       </c>
@@ -2657,7 +2745,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="9">
         <v>81</v>
       </c>
@@ -2675,7 +2763,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="9">
         <v>82</v>
       </c>
@@ -2693,7 +2781,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="9">
         <v>83</v>
       </c>
@@ -2711,7 +2799,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="9">
         <v>85</v>
       </c>
@@ -2729,7 +2817,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="9">
         <v>86</v>
       </c>
@@ -2747,7 +2835,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="9">
         <v>87</v>
       </c>
@@ -2765,7 +2853,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="9">
         <v>89</v>
       </c>
@@ -2783,7 +2871,7 @@
       </c>
       <c r="F77" s="7"/>
     </row>
-    <row r="78" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="9">
         <v>90</v>
       </c>
@@ -2801,7 +2889,7 @@
       </c>
       <c r="F78" s="7"/>
     </row>
-    <row r="79" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="9">
         <v>91</v>
       </c>
@@ -2819,7 +2907,7 @@
       </c>
       <c r="F79" s="7"/>
     </row>
-    <row r="80" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="9">
         <v>92</v>
       </c>
@@ -2837,7 +2925,7 @@
       </c>
       <c r="F80" s="7"/>
     </row>
-    <row r="81" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="9">
         <v>93</v>
       </c>
@@ -2855,7 +2943,7 @@
       </c>
       <c r="F81" s="7"/>
     </row>
-    <row r="82" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="9">
         <v>94</v>
       </c>
@@ -2873,7 +2961,7 @@
       </c>
       <c r="F82" s="7"/>
     </row>
-    <row r="83" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="9">
         <v>95</v>
       </c>
@@ -2893,7 +2981,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="9">
         <v>96</v>
       </c>
@@ -2911,7 +2999,7 @@
       </c>
       <c r="F84" s="7"/>
     </row>
-    <row r="85" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="9">
         <v>97</v>
       </c>
@@ -2929,7 +3017,7 @@
       </c>
       <c r="F85" s="7"/>
     </row>
-    <row r="86" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="9">
         <v>98</v>
       </c>
@@ -2947,7 +3035,7 @@
       </c>
       <c r="F86" s="7"/>
     </row>
-    <row r="87" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="9">
         <v>99</v>
       </c>
@@ -2965,7 +3053,7 @@
       </c>
       <c r="F87" s="7"/>
     </row>
-    <row r="88" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="9">
         <v>100</v>
       </c>
@@ -2983,7 +3071,7 @@
       </c>
       <c r="F88" s="7"/>
     </row>
-    <row r="89" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="9">
         <v>101</v>
       </c>
@@ -3001,7 +3089,7 @@
       </c>
       <c r="F89" s="7"/>
     </row>
-    <row r="90" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="9">
         <v>102</v>
       </c>
@@ -3019,7 +3107,7 @@
       </c>
       <c r="F90" s="7"/>
     </row>
-    <row r="91" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="9">
         <v>103</v>
       </c>
@@ -3037,7 +3125,7 @@
       </c>
       <c r="F91" s="7"/>
     </row>
-    <row r="92" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="9">
         <v>104</v>
       </c>
@@ -3055,7 +3143,7 @@
       </c>
       <c r="F92" s="7"/>
     </row>
-    <row r="93" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="9">
         <v>105</v>
       </c>
@@ -3073,7 +3161,7 @@
       </c>
       <c r="F93" s="7"/>
     </row>
-    <row r="94" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="9">
         <v>106</v>
       </c>
@@ -3091,7 +3179,7 @@
       </c>
       <c r="F94" s="7"/>
     </row>
-    <row r="95" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="9">
         <v>107</v>
       </c>
@@ -3109,7 +3197,7 @@
       </c>
       <c r="F95" s="7"/>
     </row>
-    <row r="96" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="9">
         <v>108</v>
       </c>
@@ -3127,7 +3215,7 @@
       </c>
       <c r="F96" s="7"/>
     </row>
-    <row r="97" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="9">
         <v>109</v>
       </c>
@@ -3145,7 +3233,7 @@
       </c>
       <c r="F97" s="7"/>
     </row>
-    <row r="98" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="9">
         <v>110</v>
       </c>
@@ -3163,7 +3251,7 @@
       </c>
       <c r="F98" s="7"/>
     </row>
-    <row r="99" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="9">
         <v>111</v>
       </c>
@@ -3181,7 +3269,7 @@
       </c>
       <c r="F99" s="7"/>
     </row>
-    <row r="100" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="9">
         <v>112</v>
       </c>
@@ -3199,7 +3287,7 @@
       </c>
       <c r="F100" s="7"/>
     </row>
-    <row r="101" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="9">
         <v>113</v>
       </c>
@@ -3217,7 +3305,7 @@
       </c>
       <c r="F101" s="7"/>
     </row>
-    <row r="102" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="9">
         <v>114</v>
       </c>
@@ -3235,7 +3323,7 @@
       </c>
       <c r="F102" s="7"/>
     </row>
-    <row r="103" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="9">
         <v>115</v>
       </c>
@@ -3253,7 +3341,7 @@
       </c>
       <c r="F103" s="10"/>
     </row>
-    <row r="104" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="9">
         <v>116</v>
       </c>
@@ -3269,7 +3357,7 @@
       </c>
       <c r="F104" s="7"/>
     </row>
-    <row r="105" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="9">
         <v>117</v>
       </c>
@@ -3287,7 +3375,7 @@
       </c>
       <c r="F105" s="7"/>
     </row>
-    <row r="106" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="9">
         <v>118</v>
       </c>
@@ -3305,7 +3393,7 @@
       </c>
       <c r="F106" s="7"/>
     </row>
-    <row r="107" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="9">
         <v>119</v>
       </c>
@@ -3325,7 +3413,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="108" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="9">
         <v>120</v>
       </c>
@@ -3343,7 +3431,7 @@
       </c>
       <c r="F108" s="6"/>
     </row>
-    <row r="109" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="9">
         <v>121</v>
       </c>
@@ -3361,7 +3449,7 @@
       </c>
       <c r="F109" s="6"/>
     </row>
-    <row r="110" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="9">
         <v>122</v>
       </c>
@@ -3379,7 +3467,7 @@
       </c>
       <c r="F110" s="6"/>
     </row>
-    <row r="111" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="9">
         <v>123</v>
       </c>
@@ -3397,7 +3485,7 @@
       </c>
       <c r="F111" s="6"/>
     </row>
-    <row r="112" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="9">
         <v>124</v>
       </c>
@@ -3415,7 +3503,7 @@
       </c>
       <c r="F112" s="6"/>
     </row>
-    <row r="113" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="9">
         <v>125</v>
       </c>
@@ -3433,7 +3521,7 @@
       </c>
       <c r="F113" s="6"/>
     </row>
-    <row r="114" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="9">
         <v>126</v>
       </c>
@@ -3451,7 +3539,7 @@
       </c>
       <c r="F114" s="6"/>
     </row>
-    <row r="115" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="9">
         <v>127</v>
       </c>
@@ -3469,7 +3557,7 @@
       </c>
       <c r="F115" s="6"/>
     </row>
-    <row r="116" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="9">
         <v>128</v>
       </c>
@@ -3487,15 +3575,141 @@
       </c>
       <c r="F116" s="6"/>
     </row>
+    <row r="117" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="9">
+        <v>129</v>
+      </c>
+      <c r="B117" s="17" t="s">
+        <v>241</v>
+      </c>
+      <c r="C117" s="17"/>
+      <c r="D117" s="17"/>
+      <c r="E117" s="17"/>
+      <c r="F117" s="18" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="9">
+        <v>130</v>
+      </c>
+      <c r="B118" s="17" t="s">
+        <v>243</v>
+      </c>
+      <c r="C118" s="17"/>
+      <c r="D118" s="17" t="s">
+        <v>244</v>
+      </c>
+      <c r="E118" s="17"/>
+      <c r="F118" s="18" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="9">
+        <v>131</v>
+      </c>
+      <c r="B119" s="17" t="s">
+        <v>246</v>
+      </c>
+      <c r="C119" s="17"/>
+      <c r="D119" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="E119" s="17"/>
+      <c r="F119" s="18" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="9">
+        <v>132</v>
+      </c>
+      <c r="B120" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="C120" s="17"/>
+      <c r="D120" s="17" t="s">
+        <v>244</v>
+      </c>
+      <c r="E120" s="17"/>
+      <c r="F120" s="18" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="9">
+        <v>133</v>
+      </c>
+      <c r="B121" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="C121" s="17"/>
+      <c r="D121" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="E121" s="17"/>
+      <c r="F121" s="18" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="9">
+        <v>134</v>
+      </c>
+      <c r="B122" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="C122" s="17"/>
+      <c r="D122" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="E122" s="17"/>
+      <c r="F122" s="18" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="9">
+        <v>135</v>
+      </c>
+      <c r="B123" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C123" s="17"/>
+      <c r="D123" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="E123" s="17"/>
+      <c r="F123" s="18" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="9">
+        <v>136</v>
+      </c>
+      <c r="B124" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="C124" s="17"/>
+      <c r="D124" s="17" t="s">
+        <v>244</v>
+      </c>
+      <c r="E124" s="17"/>
+      <c r="F124" s="18" t="s">
+        <v>258</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{010E3364-7D39-4334-B684-BC5F9F35E73D}"/>
-  <sortState ref="A2:F131">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F131">
     <sortCondition ref="A1"/>
   </sortState>
   <conditionalFormatting sqref="C1">
     <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C1048576">
+  <conditionalFormatting sqref="C1:C116 C125:C1048576">
     <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3505,17 +3719,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34493AF7-05B4-49AB-A091-004D07D6434D}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>179</v>
       </c>
@@ -3535,7 +3749,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="9">
         <v>1</v>
       </c>
@@ -3551,10 +3765,8 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
